--- a/artfynd/A 50274-2025 artfynd.xlsx
+++ b/artfynd/A 50274-2025 artfynd.xlsx
@@ -675,43 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131411651</v>
+        <v>131411559</v>
       </c>
       <c r="B2" t="n">
-        <v>57907</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Börsåsen, Börsåsen, Jmt</t>
@@ -721,7 +713,7 @@
         <v>520303</v>
       </c>
       <c r="R2" t="n">
-        <v>7055171</v>
+        <v>7055185</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran med spår av kådaflöde.</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -820,42 +807,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131410491</v>
+        <v>131413627</v>
       </c>
       <c r="B3" t="n">
-        <v>57907</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -863,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520323</v>
+        <v>520345</v>
       </c>
       <c r="R3" t="n">
-        <v>7055218</v>
+        <v>7055145</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -908,12 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, möjligen på gränsen till färska, längs flera meter på en gran.</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,6 +899,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -942,12 +920,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -965,10 +943,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131411559</v>
+        <v>131410491</v>
       </c>
       <c r="B4" t="n">
-        <v>79269</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,34 +954,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Börsåsen, Börsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520303</v>
+        <v>520323</v>
       </c>
       <c r="R4" t="n">
-        <v>7055185</v>
+        <v>7055218</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1035,7 +1021,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1045,7 +1031,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, möjligen på gränsen till färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,12 +1065,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1100,7 +1091,7 @@
         <v>131410873</v>
       </c>
       <c r="B5" t="n">
-        <v>57907</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1242,10 +1233,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131413627</v>
+        <v>131411651</v>
       </c>
       <c r="B6" t="n">
-        <v>79269</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,26 +1244,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1280,13 +1276,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520345</v>
+        <v>520303</v>
       </c>
       <c r="R6" t="n">
-        <v>7055145</v>
+        <v>7055171</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1315,7 +1311,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1325,7 +1321,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran med spår av kådaflöde.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,7 +1335,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 50274-2025 artfynd.xlsx
+++ b/artfynd/A 50274-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -804,6 +809,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131411559</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -940,6 +950,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131413627</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1085,6 +1100,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131410491</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1230,6 +1250,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131410873</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1375,8 +1400,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131411651</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>